--- a/product_selector_out/STM32F7 series.xlsx
+++ b/product_selector_out/STM32F7 series.xlsx
@@ -59784,7 +59784,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59938,7 +59938,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -60092,7 +60092,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -60246,7 +60246,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -60400,7 +60400,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -60554,7 +60554,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -60708,7 +60708,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -60862,7 +60862,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -61016,7 +61016,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -61170,7 +61170,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -61324,7 +61324,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -61478,7 +61478,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -61610,7 +61610,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -61720,7 +61720,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -61874,7 +61874,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -62050,7 +62050,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -62182,7 +62182,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -62292,7 +62292,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -62446,7 +62446,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -62622,7 +62622,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -62754,7 +62754,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -62864,7 +62864,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -62974,7 +62974,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63128,7 +63128,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63260,7 +63260,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63326,7 +63326,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63436,7 +63436,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63546,7 +63546,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63656,7 +63656,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63722,7 +63722,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63788,7 +63788,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63854,7 +63854,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63964,7 +63964,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -64118,7 +64118,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -64250,7 +64250,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -64404,7 +64404,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -64580,7 +64580,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -64712,7 +64712,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -64822,7 +64822,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -64976,7 +64976,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -65108,7 +65108,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -65218,7 +65218,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -65328,7 +65328,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -65438,7 +65438,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -65592,7 +65592,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -65724,7 +65724,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -65834,7 +65834,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -65944,7 +65944,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66076,7 +66076,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66208,7 +66208,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66318,7 +66318,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66428,7 +66428,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66560,7 +66560,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66670,7 +66670,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66802,7 +66802,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -66912,7 +66912,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67022,7 +67022,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67132,7 +67132,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67242,7 +67242,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67374,7 +67374,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67484,7 +67484,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67616,7 +67616,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67748,7 +67748,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -67902,7 +67902,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -68056,7 +68056,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -68210,7 +68210,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -68364,7 +68364,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -68518,7 +68518,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -68672,7 +68672,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -68826,7 +68826,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -68980,7 +68980,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -69112,7 +69112,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -69244,7 +69244,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -69376,7 +69376,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -69508,7 +69508,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -69640,7 +69640,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -69772,7 +69772,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -69904,7 +69904,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -70036,7 +70036,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -70168,7 +70168,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -70300,7 +70300,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -70432,7 +70432,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -70564,7 +70564,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -70696,7 +70696,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -70828,7 +70828,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -70960,7 +70960,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F7 series.xlsx
+++ b/product_selector_out/STM32F7 series.xlsx
@@ -24734,7 +24734,7 @@
       </c>
       <c r="AA82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="4" t="inlineStr">
@@ -30803,9 +30803,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="9" t="inlineStr">
@@ -31140,9 +31140,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="9" t="inlineStr">
@@ -31477,9 +31477,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="9" t="inlineStr">
@@ -31814,9 +31814,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="9" t="inlineStr">
@@ -32151,9 +32151,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="9" t="inlineStr">
@@ -32488,9 +32488,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="9" t="inlineStr">
@@ -32825,9 +32825,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="9" t="inlineStr">
@@ -33162,9 +33162,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="9" t="inlineStr">
@@ -33499,9 +33499,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="9" t="inlineStr">
@@ -33836,9 +33836,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="9" t="inlineStr">
@@ -34173,9 +34173,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB22" s="9" t="inlineStr">
@@ -34510,9 +34510,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB23" s="9" t="inlineStr">
@@ -35521,9 +35521,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA26" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB26" s="9" t="inlineStr">
@@ -35858,9 +35858,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB27" s="9" t="inlineStr">
@@ -36869,9 +36869,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB30" s="9" t="inlineStr">
@@ -37206,9 +37206,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB31" s="9" t="inlineStr">
@@ -38554,9 +38554,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA35" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB35" s="9" t="inlineStr">
@@ -41924,9 +41924,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA45" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB45" s="9" t="inlineStr">
@@ -42598,9 +42598,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA47" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB47" s="9" t="inlineStr">
@@ -42935,9 +42935,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA48" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB48" s="9" t="inlineStr">
@@ -43946,9 +43946,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA51" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB51" s="9" t="inlineStr">
@@ -45631,9 +45631,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA56" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB56" s="9" t="inlineStr">
@@ -46642,9 +46642,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA59" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB59" s="9" t="inlineStr">
@@ -46979,9 +46979,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA60" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB60" s="9" t="inlineStr">
@@ -47990,9 +47990,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA63" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA63" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB63" s="9" t="inlineStr">
@@ -48664,9 +48664,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA65" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB65" s="9" t="inlineStr">
@@ -50349,9 +50349,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA70" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB70" s="9" t="inlineStr">
@@ -51023,9 +51023,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA72" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB72" s="9" t="inlineStr">
@@ -51697,9 +51697,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA74" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB74" s="9" t="inlineStr">
@@ -52034,9 +52034,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA75" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB75" s="9" t="inlineStr">
@@ -52371,9 +52371,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA76" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB76" s="9" t="inlineStr">
@@ -52708,9 +52708,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA77" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB77" s="9" t="inlineStr">
@@ -53045,9 +53045,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA78" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB78" s="9" t="inlineStr">
@@ -53382,9 +53382,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA79" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB79" s="9" t="inlineStr">
@@ -53719,9 +53719,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA80" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB80" s="9" t="inlineStr">
@@ -54056,9 +54056,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA81" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB81" s="9" t="inlineStr">
@@ -54393,9 +54393,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA82" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AA82" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB82" s="9" t="inlineStr">
@@ -54730,9 +54730,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA83" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB83" s="9" t="inlineStr">
@@ -55067,9 +55067,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA84" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB84" s="9" t="inlineStr">
@@ -55374,14 +55374,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U85" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V85" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W85" s="9" t="inlineStr">
@@ -55404,9 +55404,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA85" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB85" s="9" t="inlineStr">
@@ -55711,14 +55711,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U86" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V86" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W86" s="9" t="inlineStr">
@@ -55741,9 +55741,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA86" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB86" s="9" t="inlineStr">
@@ -56078,9 +56078,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA87" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB87" s="9" t="inlineStr">
@@ -56415,9 +56415,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA88" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB88" s="9" t="inlineStr">
@@ -56752,9 +56752,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA89" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB89" s="9" t="inlineStr">
@@ -57089,9 +57089,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA90" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB90" s="9" t="inlineStr">
@@ -57396,14 +57396,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U91" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V91" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W91" s="9" t="inlineStr">
@@ -57426,9 +57426,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA91" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB91" s="9" t="inlineStr">
@@ -57763,9 +57763,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA92" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB92" s="9" t="inlineStr">
@@ -58100,9 +58100,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA93" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB93" s="9" t="inlineStr">
@@ -58407,14 +58407,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U94" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V94" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W94" s="9" t="inlineStr">
@@ -58437,9 +58437,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA94" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB94" s="9" t="inlineStr">
@@ -58774,9 +58774,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA95" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB95" s="9" t="inlineStr">
@@ -59111,9 +59111,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA96" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB96" s="9" t="inlineStr">
@@ -59418,14 +59418,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U97" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V97" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W97" s="9" t="inlineStr">
@@ -59448,9 +59448,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA97" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB97" s="9" t="inlineStr">

--- a/product_selector_out/STM32F7 series.xlsx
+++ b/product_selector_out/STM32F7 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO97"/>
+  <dimension ref="A1:BP97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.61328125" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1010,6 +1016,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -1681,6 +1693,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -2018,6 +2035,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -2355,6 +2377,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -2692,6 +2719,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -3029,6 +3061,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -3366,6 +3403,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -3703,6 +3745,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -4040,6 +4087,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -4377,6 +4429,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -4714,6 +4771,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -5051,6 +5113,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -5388,6 +5455,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -5725,6 +5797,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -6062,6 +6139,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -6399,6 +6481,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -6736,6 +6823,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -7073,6 +7165,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -7410,6 +7507,11 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -7747,6 +7849,11 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -8084,6 +8191,11 @@
       </c>
       <c r="BO32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -8421,6 +8533,11 @@
       </c>
       <c r="BO33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -8758,6 +8875,11 @@
       </c>
       <c r="BO34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -9095,6 +9217,11 @@
       </c>
       <c r="BO35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -9432,6 +9559,11 @@
       </c>
       <c r="BO36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f730i8.pdf</t>
         </is>
       </c>
@@ -9769,6 +9901,11 @@
       </c>
       <c r="BO37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f750n8.pdf</t>
         </is>
       </c>
@@ -10106,6 +10243,11 @@
       </c>
       <c r="BO38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f750n8.pdf</t>
         </is>
       </c>
@@ -10443,6 +10585,11 @@
       </c>
       <c r="BO39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f750n8.pdf</t>
         </is>
       </c>
@@ -10780,6 +10927,11 @@
       </c>
       <c r="BO40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f730i8.pdf</t>
         </is>
       </c>
@@ -11117,6 +11269,11 @@
       </c>
       <c r="BO41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f730i8.pdf</t>
         </is>
       </c>
@@ -11454,6 +11611,11 @@
       </c>
       <c r="BO42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f730i8.pdf</t>
         </is>
       </c>
@@ -11791,6 +11953,11 @@
       </c>
       <c r="BO43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -12128,6 +12295,11 @@
       </c>
       <c r="BO44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -12465,6 +12637,11 @@
       </c>
       <c r="BO45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -12802,6 +12979,11 @@
       </c>
       <c r="BO46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -13139,6 +13321,11 @@
       </c>
       <c r="BO47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -13476,6 +13663,11 @@
       </c>
       <c r="BO48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -13813,6 +14005,11 @@
       </c>
       <c r="BO49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -14150,6 +14347,11 @@
       </c>
       <c r="BO50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -14487,6 +14689,11 @@
       </c>
       <c r="BO51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -14824,6 +15031,11 @@
       </c>
       <c r="BO52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -15161,6 +15373,11 @@
       </c>
       <c r="BO53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -15498,6 +15715,11 @@
       </c>
       <c r="BO54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -15835,6 +16057,11 @@
       </c>
       <c r="BO55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -16172,6 +16399,11 @@
       </c>
       <c r="BO56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f777bi.pdf</t>
         </is>
       </c>
@@ -16509,6 +16741,11 @@
       </c>
       <c r="BO57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -16846,6 +17083,11 @@
       </c>
       <c r="BO58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -17183,6 +17425,11 @@
       </c>
       <c r="BO59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -17520,6 +17767,11 @@
       </c>
       <c r="BO60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -17857,6 +18109,11 @@
       </c>
       <c r="BO61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -18194,6 +18451,11 @@
       </c>
       <c r="BO62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -18531,6 +18793,11 @@
       </c>
       <c r="BO63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -18868,6 +19135,11 @@
       </c>
       <c r="BO64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -19205,6 +19477,11 @@
       </c>
       <c r="BO65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -19542,6 +19819,11 @@
       </c>
       <c r="BO66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -19879,6 +20161,11 @@
       </c>
       <c r="BO67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -20216,6 +20503,11 @@
       </c>
       <c r="BO68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -20553,6 +20845,11 @@
       </c>
       <c r="BO69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -20890,6 +21187,11 @@
       </c>
       <c r="BO70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -21227,6 +21529,11 @@
       </c>
       <c r="BO71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -21564,6 +21871,11 @@
       </c>
       <c r="BO72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -21901,6 +22213,11 @@
       </c>
       <c r="BO73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -22238,6 +22555,11 @@
       </c>
       <c r="BO74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -22575,6 +22897,11 @@
       </c>
       <c r="BO75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -22912,6 +23239,11 @@
       </c>
       <c r="BO76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -23249,6 +23581,11 @@
       </c>
       <c r="BO77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -23586,6 +23923,11 @@
       </c>
       <c r="BO78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -23923,6 +24265,11 @@
       </c>
       <c r="BO79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -24260,6 +24607,11 @@
       </c>
       <c r="BO80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -24597,6 +24949,11 @@
       </c>
       <c r="BO81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -24934,6 +25291,11 @@
       </c>
       <c r="BO82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -25271,6 +25633,11 @@
       </c>
       <c r="BO83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -25608,6 +25975,11 @@
       </c>
       <c r="BO84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -25945,6 +26317,11 @@
       </c>
       <c r="BO85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f756bg.pdf</t>
         </is>
       </c>
@@ -26282,6 +26659,11 @@
       </c>
       <c r="BO86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f756bg.pdf</t>
         </is>
       </c>
@@ -26619,6 +27001,11 @@
       </c>
       <c r="BO87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -26956,6 +27343,11 @@
       </c>
       <c r="BO88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -27293,6 +27685,11 @@
       </c>
       <c r="BO89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -27630,6 +28027,11 @@
       </c>
       <c r="BO90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -27967,6 +28369,11 @@
       </c>
       <c r="BO91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f756bg.pdf</t>
         </is>
       </c>
@@ -28304,6 +28711,11 @@
       </c>
       <c r="BO92" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP92" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -28641,6 +29053,11 @@
       </c>
       <c r="BO93" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -28978,6 +29395,11 @@
       </c>
       <c r="BO94" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f756bg.pdf</t>
         </is>
       </c>
@@ -29315,6 +29737,11 @@
       </c>
       <c r="BO95" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP95" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -29652,6 +30079,11 @@
       </c>
       <c r="BO96" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP96" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -29989,12 +30421,17 @@
       </c>
       <c r="BO97" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP97" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f756bg.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -30017,12 +30454,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -30037,9 +30476,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -30161,7 +30599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO97"/>
+  <dimension ref="A1:BP97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30231,6 +30669,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30574,6 +31013,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -30671,6 +31115,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -31003,7 +31448,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31340,7 +31790,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31677,7 +32132,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32014,7 +32474,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32351,7 +32816,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32688,7 +33158,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33025,7 +33500,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33362,7 +33842,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33699,7 +34184,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34036,7 +34526,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34373,7 +34868,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34710,7 +35210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35047,7 +35552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35384,7 +35894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35721,7 +36236,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36058,7 +36578,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36395,7 +36920,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36732,7 +37262,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37069,7 +37604,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
+      <c r="BO30" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37406,7 +37946,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO31" s="6" t="inlineStr">
+      <c r="BO31" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37743,7 +38288,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO32" s="6" t="inlineStr">
+      <c r="BO32" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38080,7 +38630,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO33" s="6" t="inlineStr">
+      <c r="BO33" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38417,7 +38972,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO34" s="6" t="inlineStr">
+      <c r="BO34" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38754,7 +39314,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO35" s="6" t="inlineStr">
+      <c r="BO35" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39091,7 +39656,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO36" s="6" t="inlineStr">
+      <c r="BO36" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39428,7 +39998,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO37" s="6" t="inlineStr">
+      <c r="BO37" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39765,7 +40340,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO38" s="6" t="inlineStr">
+      <c r="BO38" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40102,7 +40682,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO39" s="6" t="inlineStr">
+      <c r="BO39" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40439,7 +41024,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO40" s="6" t="inlineStr">
+      <c r="BO40" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40776,7 +41366,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO41" s="6" t="inlineStr">
+      <c r="BO41" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41113,7 +41708,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO42" s="6" t="inlineStr">
+      <c r="BO42" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41450,7 +42050,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO43" s="6" t="inlineStr">
+      <c r="BO43" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41787,7 +42392,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO44" s="6" t="inlineStr">
+      <c r="BO44" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42124,7 +42734,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO45" s="6" t="inlineStr">
+      <c r="BO45" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42461,7 +43076,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO46" s="6" t="inlineStr">
+      <c r="BO46" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42798,7 +43418,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO47" s="6" t="inlineStr">
+      <c r="BO47" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43135,7 +43760,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO48" s="6" t="inlineStr">
+      <c r="BO48" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43472,7 +44102,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO49" s="6" t="inlineStr">
+      <c r="BO49" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43809,7 +44444,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO50" s="6" t="inlineStr">
+      <c r="BO50" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44146,7 +44786,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO51" s="6" t="inlineStr">
+      <c r="BO51" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44483,7 +45128,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO52" s="6" t="inlineStr">
+      <c r="BO52" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44820,7 +45470,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO53" s="6" t="inlineStr">
+      <c r="BO53" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45157,7 +45812,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO54" s="6" t="inlineStr">
+      <c r="BO54" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45494,7 +46154,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO55" s="6" t="inlineStr">
+      <c r="BO55" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45831,7 +46496,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO56" s="6" t="inlineStr">
+      <c r="BO56" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46168,7 +46838,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO57" s="6" t="inlineStr">
+      <c r="BO57" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46505,7 +47180,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO58" s="6" t="inlineStr">
+      <c r="BO58" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46842,7 +47522,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO59" s="6" t="inlineStr">
+      <c r="BO59" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47179,7 +47864,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO60" s="6" t="inlineStr">
+      <c r="BO60" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47516,7 +48206,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO61" s="6" t="inlineStr">
+      <c r="BO61" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47853,7 +48548,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO62" s="6" t="inlineStr">
+      <c r="BO62" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48190,7 +48890,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO63" s="6" t="inlineStr">
+      <c r="BO63" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48527,7 +49232,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO64" s="6" t="inlineStr">
+      <c r="BO64" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48864,7 +49574,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO65" s="6" t="inlineStr">
+      <c r="BO65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49201,7 +49916,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO66" s="6" t="inlineStr">
+      <c r="BO66" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49538,7 +50258,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO67" s="6" t="inlineStr">
+      <c r="BO67" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49875,7 +50600,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO68" s="6" t="inlineStr">
+      <c r="BO68" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50212,7 +50942,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO69" s="6" t="inlineStr">
+      <c r="BO69" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50549,7 +51284,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO70" s="6" t="inlineStr">
+      <c r="BO70" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50886,7 +51626,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO71" s="6" t="inlineStr">
+      <c r="BO71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51223,7 +51968,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO72" s="6" t="inlineStr">
+      <c r="BO72" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51560,7 +52310,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO73" s="6" t="inlineStr">
+      <c r="BO73" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51897,7 +52652,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO74" s="6" t="inlineStr">
+      <c r="BO74" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52234,7 +52994,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO75" s="6" t="inlineStr">
+      <c r="BO75" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52571,7 +53336,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO76" s="6" t="inlineStr">
+      <c r="BO76" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52908,7 +53678,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO77" s="6" t="inlineStr">
+      <c r="BO77" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53245,7 +54020,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO78" s="6" t="inlineStr">
+      <c r="BO78" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53582,7 +54362,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO79" s="6" t="inlineStr">
+      <c r="BO79" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53919,7 +54704,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO80" s="6" t="inlineStr">
+      <c r="BO80" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54256,7 +55046,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO81" s="6" t="inlineStr">
+      <c r="BO81" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54593,7 +55388,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO82" s="6" t="inlineStr">
+      <c r="BO82" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54930,7 +55730,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO83" s="6" t="inlineStr">
+      <c r="BO83" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55267,7 +56072,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO84" s="6" t="inlineStr">
+      <c r="BO84" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55604,7 +56414,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO85" s="6" t="inlineStr">
+      <c r="BO85" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55941,7 +56756,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO86" s="6" t="inlineStr">
+      <c r="BO86" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56278,7 +57098,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO87" s="6" t="inlineStr">
+      <c r="BO87" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56615,7 +57440,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO88" s="6" t="inlineStr">
+      <c r="BO88" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56952,7 +57782,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO89" s="6" t="inlineStr">
+      <c r="BO89" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57289,7 +58124,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO90" s="6" t="inlineStr">
+      <c r="BO90" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57626,7 +58466,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO91" s="6" t="inlineStr">
+      <c r="BO91" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57963,7 +58808,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO92" s="6" t="inlineStr">
+      <c r="BO92" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP92" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58300,7 +59150,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO93" s="6" t="inlineStr">
+      <c r="BO93" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58637,7 +59492,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO94" s="6" t="inlineStr">
+      <c r="BO94" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58974,7 +59834,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO95" s="6" t="inlineStr">
+      <c r="BO95" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP95" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59311,7 +60176,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO96" s="6" t="inlineStr">
+      <c r="BO96" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP96" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59648,7 +60518,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO97" s="6" t="inlineStr">
+      <c r="BO97" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP97" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59656,8 +60531,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
